--- a/settlements/keel/2026-01/keel_settlement_january_2026.xlsx
+++ b/settlements/keel/2026-01/keel_settlement_january_2026.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -501,130 +501,140 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>28435.59</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>28435.59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-01-01 → 2026-01-31 (31 days)</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ethereum=24358292</t>
+          <t>2026-01-01 → 2026-01-31 (31 days)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-10T21:03:25+00:00</t>
+          <t>ethereum=24358292</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-10T21:03:25+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/settlements/keel/2026-01/keel_settlement_january_2026.xlsx
+++ b/settlements/keel/2026-01/keel_settlement_january_2026.xlsx
@@ -624,7 +624,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-10T21:03:25+00:00</t>
+          <t>2026-07-03T07:02:15+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/keel/2026-01/keel_settlement_january_2026.xlsx
+++ b/settlements/keel/2026-01/keel_settlement_january_2026.xlsx
@@ -624,7 +624,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-03T07:02:15+00:00</t>
+          <t>2026-07-07T14:51:52+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/keel/2026-01/keel_settlement_january_2026.xlsx
+++ b/settlements/keel/2026-01/keel_settlement_january_2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -624,7 +624,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-07T14:51:52+00:00</t>
+          <t>2026-07-14T09:33:53+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/keel/2026-01/keel_settlement_january_2026.xlsx
+++ b/settlements/keel/2026-01/keel_settlement_january_2026.xlsx
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>28435.59</v>
+        <v>28500.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>28435.59</v>
+        <v>28500.23</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-14T09:33:53+00:00</t>
+          <t>2026-07-15T11:04:30+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/keel/2026-01/keel_settlement_january_2026.xlsx
+++ b/settlements/keel/2026-01/keel_settlement_january_2026.xlsx
@@ -849,7 +849,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
+          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>
